--- a/BVSimulationFiles/30.xlsx
+++ b/BVSimulationFiles/30.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1 Copy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -414,75 +414,63 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.002791666666666667</v>
+        <v>0.00335</v>
       </c>
       <c r="D1" t="n">
-        <v>0.005583333333333333</v>
+        <v>0.0067</v>
       </c>
       <c r="E1" t="n">
-        <v>0.008375</v>
+        <v>0.01005</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01116666666666667</v>
+        <v>0.0134</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01395833333333333</v>
+        <v>0.01675</v>
       </c>
       <c r="H1" t="n">
-        <v>0.01675</v>
+        <v>0.0201</v>
       </c>
       <c r="I1" t="n">
-        <v>0.01954166666666667</v>
+        <v>0.02345</v>
       </c>
       <c r="J1" t="n">
-        <v>0.02233333333333333</v>
+        <v>0.0268</v>
       </c>
       <c r="K1" t="n">
-        <v>0.025125</v>
+        <v>0.03015</v>
       </c>
       <c r="L1" t="n">
-        <v>0.02791666666666667</v>
+        <v>0.0335</v>
       </c>
       <c r="M1" t="n">
-        <v>0.03070833333333333</v>
+        <v>0.03685</v>
       </c>
       <c r="N1" t="n">
-        <v>0.0335</v>
+        <v>0.0402</v>
       </c>
       <c r="O1" t="n">
-        <v>0.03629166666666667</v>
+        <v>0.04355</v>
       </c>
       <c r="P1" t="n">
-        <v>0.03908333333333333</v>
+        <v>0.0469</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.041875</v>
+        <v>0.05025</v>
       </c>
       <c r="R1" t="n">
-        <v>0.04466666666666667</v>
+        <v>0.0536</v>
       </c>
       <c r="S1" t="n">
-        <v>0.04745833333333333</v>
+        <v>0.05695</v>
       </c>
       <c r="T1" t="n">
-        <v>0.05025</v>
+        <v>0.0603</v>
       </c>
       <c r="U1" t="n">
-        <v>0.05304166666666667</v>
+        <v>0.06365</v>
       </c>
       <c r="V1" t="n">
-        <v>0.05583333333333333</v>
-      </c>
-      <c r="W1" t="n">
-        <v>0.058625</v>
-      </c>
-      <c r="X1" t="n">
-        <v>0.06141666666666667</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>0.06420833333333334</v>
-      </c>
-      <c r="Z1" t="n">
         <v>0.067</v>
       </c>
     </row>
